--- a/01_Input/00_CO Validation/South Africa - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/South Africa - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="1077" documentId="11_04BEB1641D39DF421FD57979ED4D65D0783B1080" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3FD51C-2E5F-4D43-9541-444B5477A676}"/>
+  <xr:revisionPtr revIDLastSave="1078" documentId="11_04BEB1641D39DF421FD57979ED4D65D0783B1080" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A71C16A-2FE1-4469-89FC-BD5CE34C2BC9}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="249">
   <si>
     <t>Project ID</t>
   </si>
@@ -270,9 +270,6 @@
   </si>
   <si>
     <t>50 (20 female / 30 male)</t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>Number of public and private sector and women-led energy civil society organizations (CSOs) trained on energy transition (disaggregated by gender), inclusive of amplifying the voice of women in the JET discourse</t>
@@ -810,6 +807,9 @@
   </si>
   <si>
     <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
   <si>
     <t>Any other type of beneficiary (please specify justification in Notes)</t>
@@ -2345,11 +2345,9 @@
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
       <c r="D16" s="36"/>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="54"/>
+      <c r="F16" s="60" t="s">
         <v>76</v>
-      </c>
-      <c r="F16" s="60" t="s">
-        <v>77</v>
       </c>
       <c r="G16" s="65">
         <v>0</v>
@@ -2358,7 +2356,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J16" s="36"/>
       <c r="K16" s="39">
@@ -2388,7 +2386,7 @@
         <v>60</v>
       </c>
       <c r="F17" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G17" s="65">
         <v>0</v>
@@ -2397,7 +2395,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="39">
@@ -2425,7 +2423,7 @@
       <c r="D18" s="36"/>
       <c r="E18" s="54"/>
       <c r="F18" s="60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G18" s="65">
         <v>0</v>
@@ -2544,7 +2542,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>5</v>
@@ -2562,7 +2560,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="60" customHeight="1">
@@ -2582,23 +2580,23 @@
         <v>19</v>
       </c>
       <c r="F2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>85</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="15">
         <v>7600000</v>
       </c>
       <c r="J2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="L2" s="18" t="s">
         <v>87</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="76.5">
@@ -2608,18 +2606,18 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="K3" s="19" t="s">
         <v>91</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>92</v>
       </c>
       <c r="L3" s="14"/>
     </row>
@@ -2630,7 +2628,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
@@ -2639,7 +2637,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="80"/>
       <c r="K4" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L4" s="14"/>
     </row>
@@ -2650,14 +2648,14 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="80"/>
       <c r="K5" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="14"/>
     </row>
@@ -2668,18 +2666,18 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="19" t="s">
         <v>99</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>100</v>
       </c>
       <c r="L6" s="14"/>
     </row>
@@ -2690,16 +2688,16 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="80"/>
       <c r="K7" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L7" s="14"/>
     </row>
@@ -2710,14 +2708,14 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="80"/>
       <c r="K8" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L8" s="14"/>
     </row>
@@ -2728,7 +2726,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -2744,17 +2742,17 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="14"/>
@@ -2766,17 +2764,17 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="14"/>
@@ -2788,14 +2786,14 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>116</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>117</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="19"/>
@@ -2808,14 +2806,14 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="19"/>
@@ -2828,14 +2826,14 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="19"/>
@@ -2848,7 +2846,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -2864,14 +2862,14 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>127</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="19"/>
@@ -2884,14 +2882,14 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="19"/>
@@ -2904,11 +2902,11 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -2922,7 +2920,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -2938,14 +2936,14 @@
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="19"/>
@@ -2958,14 +2956,14 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="19"/>
@@ -2978,7 +2976,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -2994,17 +2992,17 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="J23" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="K23" s="19"/>
       <c r="L23" s="14"/>
@@ -3016,17 +3014,17 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="J24" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>148</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="14"/>
@@ -3038,7 +3036,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -3054,17 +3052,17 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="J26" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="14"/>
@@ -3086,19 +3084,19 @@
         <v>45</v>
       </c>
       <c r="F27" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="H27" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>34</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K27" s="21" t="s">
         <v>35</v>
@@ -3111,10 +3109,10 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" s="22" t="s">
         <v>158</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>159</v>
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -3131,10 +3129,10 @@
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>38</v>
@@ -3159,17 +3157,17 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="I30" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L30" s="14"/>
     </row>
@@ -3180,7 +3178,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -3196,14 +3194,14 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -3216,14 +3214,14 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="I33" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -3236,14 +3234,14 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
@@ -3256,7 +3254,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
@@ -3272,7 +3270,7 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
@@ -3292,14 +3290,14 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
@@ -3312,7 +3310,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -3328,14 +3326,14 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
@@ -3348,14 +3346,14 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
@@ -3394,10 +3392,10 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -3416,10 +3414,10 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3438,10 +3436,10 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="H44" s="6">
         <v>0</v>
@@ -3463,16 +3461,16 @@
         <v>1000000</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G45" s="24"/>
       <c r="H45" s="25"/>
       <c r="I45" s="25"/>
       <c r="J45" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K45" s="26" t="s">
         <v>59</v>
@@ -3488,7 +3486,7 @@
         <v>45</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G46" s="24" t="s">
         <v>58</v>
@@ -3512,10 +3510,10 @@
         <v>19</v>
       </c>
       <c r="F47" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="G47" s="28" t="s">
         <v>197</v>
-      </c>
-      <c r="G47" s="28" t="s">
-        <v>198</v>
       </c>
       <c r="H47" s="29">
         <v>1</v>
@@ -3534,13 +3532,13 @@
       <c r="D48" s="28"/>
       <c r="E48" s="28"/>
       <c r="F48" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G48" s="28" t="s">
         <v>61</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>62</v>
@@ -3556,7 +3554,7 @@
       <c r="D49" s="28"/>
       <c r="E49" s="28"/>
       <c r="F49" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G49" s="28" t="s">
         <v>63</v>
@@ -3578,7 +3576,7 @@
       <c r="D50" s="28"/>
       <c r="E50" s="28"/>
       <c r="F50" s="28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G50" s="28" t="s">
         <v>65</v>
@@ -3600,7 +3598,7 @@
       <c r="D51" s="28"/>
       <c r="E51" s="28"/>
       <c r="F51" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="3"/>
@@ -3616,13 +3614,13 @@
       <c r="D52" s="28"/>
       <c r="E52" s="28"/>
       <c r="F52" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>67</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>68</v>
@@ -3638,10 +3636,10 @@
       <c r="D53" s="28"/>
       <c r="E53" s="28"/>
       <c r="F53" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="G53" s="28" t="s">
         <v>206</v>
-      </c>
-      <c r="G53" s="28" t="s">
-        <v>207</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
@@ -3664,7 +3662,7 @@
         <v>69</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>72</v>
@@ -3700,7 +3698,7 @@
       <c r="D56" s="28"/>
       <c r="E56" s="28"/>
       <c r="F56" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="3"/>
@@ -3716,16 +3714,16 @@
       <c r="D57" s="28"/>
       <c r="E57" s="28"/>
       <c r="F57" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J57" s="28"/>
       <c r="K57" s="28"/>
@@ -3739,13 +3737,13 @@
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J58" s="28"/>
       <c r="K58" s="28"/>
@@ -3758,10 +3756,10 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28"/>
       <c r="F59" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G59" s="28" t="s">
         <v>211</v>
-      </c>
-      <c r="G59" s="28" t="s">
-        <v>212</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3780,10 +3778,10 @@
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
       <c r="F60" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="G60" s="28" t="s">
         <v>213</v>
-      </c>
-      <c r="G60" s="28" t="s">
-        <v>214</v>
       </c>
       <c r="H60" s="2">
         <v>3</v>
@@ -3803,7 +3801,7 @@
       <c r="E61" s="28"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -3884,7 +3882,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>5</v>
@@ -3902,7 +3900,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="290.25">
@@ -3922,23 +3920,23 @@
         <v>19</v>
       </c>
       <c r="F2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>85</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="15">
         <v>7600000</v>
       </c>
       <c r="J2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="L2" s="18" t="s">
         <v>87</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="76.5">
@@ -3948,18 +3946,18 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="K3" s="19" t="s">
         <v>91</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>92</v>
       </c>
       <c r="L3" s="14"/>
     </row>
@@ -3970,7 +3968,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
@@ -3979,7 +3977,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="80"/>
       <c r="K4" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L4" s="14"/>
     </row>
@@ -3990,14 +3988,14 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="80"/>
       <c r="K5" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="14"/>
     </row>
@@ -4008,18 +4006,18 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="19" t="s">
         <v>99</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>100</v>
       </c>
       <c r="L6" s="14"/>
     </row>
@@ -4030,16 +4028,16 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="80"/>
       <c r="K7" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L7" s="14"/>
     </row>
@@ -4050,14 +4048,14 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="80"/>
       <c r="K8" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L8" s="14"/>
     </row>
@@ -4068,7 +4066,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -4084,17 +4082,17 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="14"/>
@@ -4106,17 +4104,17 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="14"/>
@@ -4128,14 +4126,14 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>116</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>117</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="19"/>
@@ -4148,14 +4146,14 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="19"/>
@@ -4168,14 +4166,14 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="19"/>
@@ -4188,7 +4186,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -4204,14 +4202,14 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>127</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="19"/>
@@ -4224,14 +4222,14 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="19"/>
@@ -4244,11 +4242,11 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -4262,7 +4260,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -4278,14 +4276,14 @@
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="19"/>
@@ -4298,14 +4296,14 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="19"/>
@@ -4318,7 +4316,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -4334,17 +4332,17 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="J23" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="K23" s="19"/>
       <c r="L23" s="14"/>
@@ -4356,17 +4354,17 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="J24" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>148</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="14"/>
@@ -4378,7 +4376,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -4394,17 +4392,17 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="J26" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="14"/>
@@ -4426,19 +4424,19 @@
         <v>45</v>
       </c>
       <c r="F27" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="H27" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>34</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K27" s="21" t="s">
         <v>35</v>
@@ -4451,10 +4449,10 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" s="22" t="s">
         <v>158</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>159</v>
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -4471,10 +4469,10 @@
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>38</v>
@@ -4499,17 +4497,17 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="I30" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L30" s="14"/>
     </row>
@@ -4520,7 +4518,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -4536,14 +4534,14 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -4556,14 +4554,14 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="I33" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -4576,14 +4574,14 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
@@ -4596,7 +4594,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
@@ -4612,7 +4610,7 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
@@ -4632,14 +4630,14 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
@@ -4652,7 +4650,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -4668,14 +4666,14 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
@@ -4688,14 +4686,14 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
@@ -4734,10 +4732,10 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -4756,10 +4754,10 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -4778,10 +4776,10 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="H44" s="6">
         <v>0</v>
@@ -4803,16 +4801,16 @@
         <v>1000000</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G45" s="24"/>
       <c r="H45" s="25"/>
       <c r="I45" s="25"/>
       <c r="J45" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K45" s="26" t="s">
         <v>59</v>
@@ -4828,7 +4826,7 @@
         <v>45</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G46" s="24" t="s">
         <v>58</v>
@@ -4852,10 +4850,10 @@
         <v>19</v>
       </c>
       <c r="F47" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="G47" s="28" t="s">
         <v>197</v>
-      </c>
-      <c r="G47" s="28" t="s">
-        <v>198</v>
       </c>
       <c r="H47" s="29">
         <v>1</v>
@@ -4874,13 +4872,13 @@
       <c r="D48" s="28"/>
       <c r="E48" s="28"/>
       <c r="F48" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G48" s="28" t="s">
         <v>61</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>62</v>
@@ -4896,7 +4894,7 @@
       <c r="D49" s="28"/>
       <c r="E49" s="28"/>
       <c r="F49" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G49" s="28" t="s">
         <v>63</v>
@@ -4918,7 +4916,7 @@
       <c r="D50" s="28"/>
       <c r="E50" s="28"/>
       <c r="F50" s="28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G50" s="28" t="s">
         <v>65</v>
@@ -4940,7 +4938,7 @@
       <c r="D51" s="28"/>
       <c r="E51" s="28"/>
       <c r="F51" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="3"/>
@@ -4956,13 +4954,13 @@
       <c r="D52" s="28"/>
       <c r="E52" s="28"/>
       <c r="F52" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>67</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>68</v>
@@ -4978,10 +4976,10 @@
       <c r="D53" s="28"/>
       <c r="E53" s="28"/>
       <c r="F53" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="G53" s="28" t="s">
         <v>206</v>
-      </c>
-      <c r="G53" s="28" t="s">
-        <v>207</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
@@ -5004,7 +5002,7 @@
         <v>69</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>72</v>
@@ -5040,7 +5038,7 @@
       <c r="D56" s="28"/>
       <c r="E56" s="28"/>
       <c r="F56" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="3"/>
@@ -5056,16 +5054,16 @@
       <c r="D57" s="28"/>
       <c r="E57" s="28"/>
       <c r="F57" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J57" s="28"/>
       <c r="K57" s="28"/>
@@ -5079,13 +5077,13 @@
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J58" s="28"/>
       <c r="K58" s="28"/>
@@ -5098,10 +5096,10 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28"/>
       <c r="F59" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G59" s="28" t="s">
         <v>211</v>
-      </c>
-      <c r="G59" s="28" t="s">
-        <v>212</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -5120,10 +5118,10 @@
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
       <c r="F60" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="G60" s="28" t="s">
         <v>213</v>
-      </c>
-      <c r="G60" s="28" t="s">
-        <v>214</v>
       </c>
       <c r="H60" s="2">
         <v>3</v>
@@ -5143,7 +5141,7 @@
       <c r="E61" s="28"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -5211,7 +5209,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="72" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5219,63 +5217,63 @@
         <v>45</v>
       </c>
       <c r="B3" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="84" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="72" t="s">
         <v>217</v>
-      </c>
-      <c r="B4" s="72" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
       <c r="A5" s="84" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="72" t="s">
         <v>219</v>
-      </c>
-      <c r="B5" s="72" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
       <c r="A6" s="84" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>221</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
       <c r="A7" s="84" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="72" t="s">
         <v>223</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
       <c r="A8" s="84" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
       <c r="A9" s="84" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="72" t="s">
         <v>226</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="84" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="85" t="s">
         <v>228</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
@@ -5283,39 +5281,39 @@
         <v>28</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
       <c r="A12" s="84" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="72" t="s">
         <v>231</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
       <c r="A13" s="84" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="85" t="s">
         <v>233</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="84" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="85" t="s">
         <v>235</v>
-      </c>
-      <c r="B14" s="85" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
       <c r="A15" s="84" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="85" t="s">
         <v>237</v>
-      </c>
-      <c r="B15" s="85" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
@@ -5323,7 +5321,7 @@
         <v>66</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
@@ -5331,31 +5329,31 @@
         <v>60</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
       <c r="A18" s="84" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="85" t="s">
         <v>241</v>
-      </c>
-      <c r="B18" s="85" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
       <c r="A19" s="84" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="85" t="s">
         <v>243</v>
-      </c>
-      <c r="B19" s="85" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
       <c r="A20" s="84" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" s="85" t="s">
         <v>245</v>
-      </c>
-      <c r="B20" s="85" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
@@ -5363,12 +5361,12 @@
         <v>19</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
       <c r="A22" s="84" t="s">
-        <v>76</v>
+        <v>247</v>
       </c>
       <c r="B22" s="85" t="s">
         <v>248</v>
@@ -5380,19 +5378,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -5417,6 +5413,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -5496,6 +5493,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -5640,22 +5642,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F11A6E-3447-4DD8-8640-39E570D1D2DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB90B757-2575-41DD-87F4-EC29D9CB0158}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EF8A23F-3390-418B-8F91-A8ECC9FCB923}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8692E424-3869-4127-BDA0-1CE08A12E29A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB90B757-2575-41DD-87F4-EC29D9CB0158}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F11A6E-3447-4DD8-8640-39E570D1D2DD}"/>
 </file>
--- a/01_Input/00_CO Validation/South Africa - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/South Africa - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28317"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="1078" documentId="11_04BEB1641D39DF421FD57979ED4D65D0783B1080" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A71C16A-2FE1-4469-89FC-BD5CE34C2BC9}"/>
+  <xr:revisionPtr revIDLastSave="1084" documentId="11_04BEB1641D39DF421FD57979ED4D65D0783B1080" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BE31FB7-38AE-4F79-9CCD-3DAE57D81BEC}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="251">
   <si>
     <t>Project ID</t>
   </si>
@@ -102,34 +102,40 @@
     <t>LED and high efficiency transformers in SA</t>
   </si>
   <si>
+    <t>https://co.pims.undp.org/project/view?id=5728</t>
+  </si>
+  <si>
+    <t>GHG Emissions Reduction</t>
+  </si>
+  <si>
+    <t>Cumulative savings of tCO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4 ktCO2 of GHG emissions due to lighting is projected to decline to 44.9 ktCO2 at EoP under business as usual and to 43.4 ktCO2 in 2030. Emissions due to transformer losses in will increase to 19.8ktCO2 at EoP (2023) and 23.1 ktCO2 in 2030 </t>
+  </si>
+  <si>
+    <t>GEF</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t>Number of households</t>
+  </si>
+  <si>
+    <t>500000 HH</t>
+  </si>
+  <si>
+    <t>South Africa Wind Energy Project (Phase II)</t>
+  </si>
+  <si>
     <t>PIMS+</t>
-  </si>
-  <si>
-    <t>GHG Emissions Reduction</t>
-  </si>
-  <si>
-    <t>Cumulative savings of tCO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4 ktCO2 of GHG emissions due to lighting is projected to decline to 44.9 ktCO2 at EoP under business as usual and to 43.4 ktCO2 in 2030. Emissions due to transformer losses in will increase to 19.8ktCO2 at EoP (2023) and 23.1 ktCO2 in 2030 </t>
-  </si>
-  <si>
-    <t>VF</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>Energy Efficiency Services</t>
-  </si>
-  <si>
-    <t>Number of households</t>
-  </si>
-  <si>
-    <t>500000 HH</t>
-  </si>
-  <si>
-    <t>South Africa Wind Energy Project (Phase II)</t>
   </si>
   <si>
     <t>Electricity Access</t>
@@ -819,7 +825,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -872,6 +878,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1114,10 +1128,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1358,6 +1373,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1368,7 +1386,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1766,7 +1785,7 @@
       <c r="B2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="84" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="7">
@@ -1785,14 +1804,16 @@
         <v>21100</v>
       </c>
       <c r="I2" s="52"/>
-      <c r="J2" s="50"/>
+      <c r="J2" s="50" t="s">
+        <v>26</v>
+      </c>
       <c r="K2" s="42"/>
       <c r="L2" s="77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="44"/>
       <c r="N2" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O2" s="44"/>
       <c r="P2" s="44"/>
@@ -1808,24 +1829,26 @@
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="53"/>
-      <c r="J3" s="50"/>
+      <c r="J3" s="50" t="s">
+        <v>26</v>
+      </c>
       <c r="K3" s="42"/>
       <c r="L3" s="77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" s="44"/>
       <c r="P3" s="44"/>
@@ -1840,44 +1863,44 @@
         <v>5256</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D4" s="8">
         <v>3554250</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="68">
         <v>74230</v>
       </c>
       <c r="I4" s="67" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K4" s="42"/>
       <c r="L4" s="77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="44"/>
       <c r="N4" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O4" s="44"/>
       <c r="P4" s="44"/>
       <c r="Q4" s="44"/>
       <c r="R4" s="44"/>
       <c r="S4" s="79" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T4" s="44"/>
       <c r="U4" s="79"/>
@@ -1899,15 +1922,15 @@
       </c>
       <c r="I5" s="37"/>
       <c r="J5" s="40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" s="42"/>
       <c r="L5" s="77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O5" s="44"/>
       <c r="P5" s="44"/>
@@ -1926,39 +1949,39 @@
         <v>19</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" s="70"/>
       <c r="I6" s="37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J6" s="40" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K6" s="42"/>
       <c r="L6" s="77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6" s="44"/>
       <c r="N6" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O6" s="44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P6" s="44"/>
       <c r="Q6" s="44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R6" s="44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S6" s="79"/>
       <c r="T6" s="44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U6" s="79"/>
     </row>
@@ -1968,45 +1991,45 @@
       <c r="C7" s="9"/>
       <c r="D7" s="35"/>
       <c r="E7" s="37" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" s="70">
         <v>1.8</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J7" s="35"/>
       <c r="K7" s="42"/>
       <c r="L7" s="77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O7" s="44"/>
       <c r="P7" s="44"/>
       <c r="Q7" s="44"/>
       <c r="R7" s="44"/>
       <c r="S7" s="79" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T7" s="44"/>
       <c r="U7" s="79"/>
     </row>
     <row r="8" spans="1:21" ht="97.5" customHeight="1">
       <c r="A8" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" s="56"/>
       <c r="D8" s="33">
@@ -2016,7 +2039,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G8" s="33">
         <v>0</v>
@@ -2025,41 +2048,41 @@
         <v>6</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K8" s="32"/>
       <c r="L8" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O8" s="44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P8" s="44"/>
       <c r="Q8" s="44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R8" s="44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S8" s="79"/>
       <c r="T8" s="44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U8" s="79"/>
     </row>
     <row r="9" spans="1:21" ht="53.25" customHeight="1">
       <c r="A9" s="54" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="54">
@@ -2069,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="64">
         <v>0</v>
@@ -2081,29 +2104,29 @@
         <v>1</v>
       </c>
       <c r="J9" s="36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K9" s="42"/>
       <c r="L9" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M9" s="44"/>
       <c r="N9" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O9" s="44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P9" s="44"/>
       <c r="Q9" s="44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R9" s="44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S9" s="79"/>
       <c r="T9" s="44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U9" s="79"/>
     </row>
@@ -2113,10 +2136,10 @@
       <c r="C10" s="28"/>
       <c r="D10" s="36"/>
       <c r="E10" s="54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G10" s="65">
         <v>24</v>
@@ -2125,18 +2148,18 @@
         <v>75</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J10" s="36"/>
       <c r="K10" s="39">
         <v>0.48</v>
       </c>
       <c r="L10" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O10" s="44"/>
       <c r="P10" s="44"/>
@@ -2152,10 +2175,10 @@
       <c r="C11" s="28"/>
       <c r="D11" s="36"/>
       <c r="E11" s="54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" s="60" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G11" s="65">
         <v>0</v>
@@ -2164,18 +2187,18 @@
         <v>25</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J11" s="36"/>
       <c r="K11" s="39">
         <v>0.4</v>
       </c>
       <c r="L11" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O11" s="44"/>
       <c r="P11" s="44"/>
@@ -2192,7 +2215,7 @@
       <c r="D12" s="36"/>
       <c r="E12" s="54"/>
       <c r="F12" s="60" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G12" s="65">
         <v>1</v>
@@ -2206,11 +2229,11 @@
       <c r="J12" s="36"/>
       <c r="K12" s="38"/>
       <c r="L12" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O12" s="44"/>
       <c r="P12" s="44"/>
@@ -2226,10 +2249,10 @@
       <c r="C13" s="28"/>
       <c r="D13" s="36"/>
       <c r="E13" s="54" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F13" s="60" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" s="65">
         <v>2</v>
@@ -2238,18 +2261,18 @@
         <v>10</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J13" s="36"/>
       <c r="K13" s="39">
         <v>0.6</v>
       </c>
       <c r="L13" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O13" s="44"/>
       <c r="P13" s="44"/>
@@ -2265,19 +2288,19 @@
       <c r="C14" s="28"/>
       <c r="D14" s="36"/>
       <c r="E14" s="54" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" s="61" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G14" s="65" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="36"/>
       <c r="K14" s="39">
@@ -2285,18 +2308,18 @@
         <v>0.5357142857142857</v>
       </c>
       <c r="L14" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M14" s="44"/>
       <c r="N14" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O14" s="44"/>
       <c r="P14" s="44"/>
       <c r="Q14" s="44"/>
       <c r="R14" s="44"/>
       <c r="S14" s="79" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="T14" s="44"/>
       <c r="U14" s="79"/>
@@ -2307,10 +2330,10 @@
       <c r="C15" s="28"/>
       <c r="D15" s="36"/>
       <c r="E15" s="54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="65">
         <v>0</v>
@@ -2319,18 +2342,18 @@
         <v>50</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="39">
         <v>0.4</v>
       </c>
       <c r="L15" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O15" s="44"/>
       <c r="P15" s="44"/>
@@ -2347,7 +2370,7 @@
       <c r="D16" s="36"/>
       <c r="E16" s="54"/>
       <c r="F16" s="60" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G16" s="65">
         <v>0</v>
@@ -2356,18 +2379,18 @@
         <v>8</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J16" s="36"/>
       <c r="K16" s="39">
         <v>1</v>
       </c>
       <c r="L16" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M16" s="44"/>
       <c r="N16" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O16" s="44"/>
       <c r="P16" s="44"/>
@@ -2383,10 +2406,10 @@
       <c r="C17" s="28"/>
       <c r="D17" s="36"/>
       <c r="E17" s="54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F17" s="61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G17" s="65">
         <v>0</v>
@@ -2395,18 +2418,18 @@
         <v>25</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="39">
         <v>0.6</v>
       </c>
       <c r="L17" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M17" s="44"/>
       <c r="N17" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O17" s="44"/>
       <c r="P17" s="44"/>
@@ -2423,7 +2446,7 @@
       <c r="D18" s="36"/>
       <c r="E18" s="54"/>
       <c r="F18" s="60" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G18" s="65">
         <v>0</v>
@@ -2437,11 +2460,11 @@
       <c r="J18" s="36"/>
       <c r="K18" s="38"/>
       <c r="L18" s="77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M18" s="44"/>
       <c r="N18" s="78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O18" s="44"/>
       <c r="P18" s="44"/>
@@ -2492,6 +2515,9 @@
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{DAD8A00F-FF72-47CD-8AAC-1B68078BF6EC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2542,7 +2568,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>5</v>
@@ -2560,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="60" customHeight="1">
@@ -2571,7 +2597,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D2" s="7">
         <v>5000000</v>
@@ -2580,23 +2606,23 @@
         <v>19</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="15">
         <v>7600000</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="76.5">
@@ -2606,18 +2632,18 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="80" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L3" s="14"/>
     </row>
@@ -2628,7 +2654,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
@@ -2637,7 +2663,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="80"/>
       <c r="K4" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L4" s="14"/>
     </row>
@@ -2648,14 +2674,14 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="80"/>
       <c r="K5" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L5" s="14"/>
     </row>
@@ -2666,18 +2692,18 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="80" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L6" s="14"/>
     </row>
@@ -2688,16 +2714,16 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="80"/>
       <c r="K7" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L7" s="14"/>
     </row>
@@ -2708,14 +2734,14 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="80"/>
       <c r="K8" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L8" s="14"/>
     </row>
@@ -2726,7 +2752,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -2742,17 +2768,17 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="14"/>
@@ -2764,17 +2790,17 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="14"/>
@@ -2786,14 +2812,14 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="19"/>
@@ -2806,14 +2832,14 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="19"/>
@@ -2826,14 +2852,14 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="19"/>
@@ -2846,7 +2872,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -2862,14 +2888,14 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="19"/>
@@ -2882,14 +2908,14 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="19"/>
@@ -2902,11 +2928,11 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -2920,7 +2946,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -2936,14 +2962,14 @@
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="19"/>
@@ -2956,14 +2982,14 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="19"/>
@@ -2976,7 +3002,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -2992,17 +3018,17 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K23" s="19"/>
       <c r="L23" s="14"/>
@@ -3014,17 +3040,17 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="14"/>
@@ -3036,7 +3062,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -3052,17 +3078,17 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="14"/>
@@ -3072,34 +3098,34 @@
         <v>5256</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D27" s="20">
         <v>3554250</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L27" s="14"/>
     </row>
@@ -3109,17 +3135,17 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="I28" s="22"/>
       <c r="J28" s="9"/>
       <c r="K28" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L28" s="14"/>
     </row>
@@ -3129,23 +3155,23 @@
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L29" s="14"/>
     </row>
@@ -3157,17 +3183,17 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L30" s="14"/>
     </row>
@@ -3178,7 +3204,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -3194,14 +3220,14 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -3214,14 +3240,14 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -3234,14 +3260,14 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
@@ -3254,7 +3280,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
@@ -3270,14 +3296,14 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
@@ -3290,14 +3316,14 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
@@ -3310,7 +3336,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -3326,14 +3352,14 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
@@ -3346,14 +3372,14 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
@@ -3362,7 +3388,7 @@
     <row r="41" spans="1:12" ht="76.5">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -3372,16 +3398,16 @@
         <v>19</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="81" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L41" s="14"/>
     </row>
@@ -3392,10 +3418,10 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -3414,10 +3440,10 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3436,10 +3462,10 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H44" s="6">
         <v>0</v>
@@ -3454,26 +3480,26 @@
     <row r="45" spans="1:12">
       <c r="A45" s="24"/>
       <c r="B45" s="24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C45" s="24"/>
       <c r="D45" s="24">
         <v>1000000</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G45" s="24"/>
       <c r="H45" s="25"/>
       <c r="I45" s="25"/>
       <c r="J45" s="24" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K45" s="26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L45" s="14"/>
     </row>
@@ -3483,13 +3509,13 @@
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
       <c r="E46" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H46" s="25">
         <v>0</v>
@@ -3510,10 +3536,10 @@
         <v>19</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H47" s="29">
         <v>1</v>
@@ -3532,16 +3558,16 @@
       <c r="D48" s="28"/>
       <c r="E48" s="28"/>
       <c r="F48" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J48" s="28"/>
       <c r="K48" s="28"/>
@@ -3554,16 +3580,16 @@
       <c r="D49" s="28"/>
       <c r="E49" s="28"/>
       <c r="F49" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J49" s="28"/>
       <c r="K49" s="28"/>
@@ -3576,10 +3602,10 @@
       <c r="D50" s="28"/>
       <c r="E50" s="28"/>
       <c r="F50" s="28" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G50" s="28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
@@ -3598,7 +3624,7 @@
       <c r="D51" s="28"/>
       <c r="E51" s="28"/>
       <c r="F51" s="26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="3"/>
@@ -3614,16 +3640,16 @@
       <c r="D52" s="28"/>
       <c r="E52" s="28"/>
       <c r="F52" s="26" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J52" s="28"/>
       <c r="K52" s="28"/>
@@ -3636,10 +3662,10 @@
       <c r="D53" s="28"/>
       <c r="E53" s="28"/>
       <c r="F53" s="28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
@@ -3659,13 +3685,13 @@
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J54" s="28"/>
       <c r="K54" s="28"/>
@@ -3679,13 +3705,13 @@
       <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J55" s="28"/>
       <c r="K55" s="28"/>
@@ -3698,7 +3724,7 @@
       <c r="D56" s="28"/>
       <c r="E56" s="28"/>
       <c r="F56" s="26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="3"/>
@@ -3714,16 +3740,16 @@
       <c r="D57" s="28"/>
       <c r="E57" s="28"/>
       <c r="F57" s="26" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J57" s="28"/>
       <c r="K57" s="28"/>
@@ -3737,13 +3763,13 @@
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J58" s="28"/>
       <c r="K58" s="28"/>
@@ -3756,10 +3782,10 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28"/>
       <c r="F59" s="28" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3778,10 +3804,10 @@
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
       <c r="F60" s="28" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H60" s="2">
         <v>3</v>
@@ -3801,7 +3827,7 @@
       <c r="E61" s="28"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -3882,7 +3908,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>5</v>
@@ -3900,7 +3926,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="290.25">
@@ -3911,7 +3937,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D2" s="7">
         <v>5000000</v>
@@ -3920,23 +3946,23 @@
         <v>19</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="15">
         <v>7600000</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="76.5">
@@ -3946,18 +3972,18 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="80" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L3" s="14"/>
     </row>
@@ -3968,7 +3994,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
@@ -3977,7 +4003,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="80"/>
       <c r="K4" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L4" s="14"/>
     </row>
@@ -3988,14 +4014,14 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="80"/>
       <c r="K5" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L5" s="14"/>
     </row>
@@ -4006,18 +4032,18 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="80" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L6" s="14"/>
     </row>
@@ -4028,16 +4054,16 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="80"/>
       <c r="K7" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L7" s="14"/>
     </row>
@@ -4048,14 +4074,14 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="80"/>
       <c r="K8" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L8" s="14"/>
     </row>
@@ -4066,7 +4092,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -4082,17 +4108,17 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="14"/>
@@ -4104,17 +4130,17 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="14"/>
@@ -4126,14 +4152,14 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="19"/>
@@ -4146,14 +4172,14 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="19"/>
@@ -4166,14 +4192,14 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="19"/>
@@ -4186,7 +4212,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -4202,14 +4228,14 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="19"/>
@@ -4222,14 +4248,14 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="19"/>
@@ -4242,11 +4268,11 @@
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -4260,7 +4286,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -4276,14 +4302,14 @@
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="19"/>
@@ -4296,14 +4322,14 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="19"/>
@@ -4316,7 +4342,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -4332,17 +4358,17 @@
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K23" s="19"/>
       <c r="L23" s="14"/>
@@ -4354,17 +4380,17 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="14"/>
@@ -4376,7 +4402,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -4392,17 +4418,17 @@
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="14"/>
@@ -4412,34 +4438,34 @@
         <v>5256</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D27" s="20">
         <v>3554250</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L27" s="14"/>
     </row>
@@ -4449,17 +4475,17 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="I28" s="22"/>
       <c r="J28" s="9"/>
       <c r="K28" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L28" s="14"/>
     </row>
@@ -4469,23 +4495,23 @@
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L29" s="14"/>
     </row>
@@ -4497,17 +4523,17 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L30" s="14"/>
     </row>
@@ -4518,7 +4544,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -4534,14 +4560,14 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -4554,14 +4580,14 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -4574,14 +4600,14 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
@@ -4594,7 +4620,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
@@ -4610,14 +4636,14 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
@@ -4630,14 +4656,14 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
@@ -4650,7 +4676,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -4666,14 +4692,14 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
@@ -4686,14 +4712,14 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
@@ -4702,7 +4728,7 @@
     <row r="41" spans="1:12" ht="76.5">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -4712,16 +4738,16 @@
         <v>19</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="81" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L41" s="14"/>
     </row>
@@ -4732,10 +4758,10 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -4754,10 +4780,10 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -4776,10 +4802,10 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H44" s="6">
         <v>0</v>
@@ -4794,26 +4820,26 @@
     <row r="45" spans="1:12">
       <c r="A45" s="24"/>
       <c r="B45" s="24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C45" s="24"/>
       <c r="D45" s="24">
         <v>1000000</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G45" s="24"/>
       <c r="H45" s="25"/>
       <c r="I45" s="25"/>
       <c r="J45" s="24" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K45" s="26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L45" s="14"/>
     </row>
@@ -4823,13 +4849,13 @@
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
       <c r="E46" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H46" s="25">
         <v>0</v>
@@ -4850,10 +4876,10 @@
         <v>19</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H47" s="29">
         <v>1</v>
@@ -4872,16 +4898,16 @@
       <c r="D48" s="28"/>
       <c r="E48" s="28"/>
       <c r="F48" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J48" s="28"/>
       <c r="K48" s="28"/>
@@ -4894,16 +4920,16 @@
       <c r="D49" s="28"/>
       <c r="E49" s="28"/>
       <c r="F49" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J49" s="28"/>
       <c r="K49" s="28"/>
@@ -4916,10 +4942,10 @@
       <c r="D50" s="28"/>
       <c r="E50" s="28"/>
       <c r="F50" s="28" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G50" s="28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
@@ -4938,7 +4964,7 @@
       <c r="D51" s="28"/>
       <c r="E51" s="28"/>
       <c r="F51" s="26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="3"/>
@@ -4954,16 +4980,16 @@
       <c r="D52" s="28"/>
       <c r="E52" s="28"/>
       <c r="F52" s="26" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J52" s="28"/>
       <c r="K52" s="28"/>
@@ -4976,10 +5002,10 @@
       <c r="D53" s="28"/>
       <c r="E53" s="28"/>
       <c r="F53" s="28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
@@ -4999,13 +5025,13 @@
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
       <c r="G54" s="30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J54" s="28"/>
       <c r="K54" s="28"/>
@@ -5019,13 +5045,13 @@
       <c r="E55" s="28"/>
       <c r="F55" s="28"/>
       <c r="G55" s="31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J55" s="28"/>
       <c r="K55" s="28"/>
@@ -5038,7 +5064,7 @@
       <c r="D56" s="28"/>
       <c r="E56" s="28"/>
       <c r="F56" s="26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="3"/>
@@ -5054,16 +5080,16 @@
       <c r="D57" s="28"/>
       <c r="E57" s="28"/>
       <c r="F57" s="26" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J57" s="28"/>
       <c r="K57" s="28"/>
@@ -5077,13 +5103,13 @@
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
       <c r="G58" s="30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J58" s="28"/>
       <c r="K58" s="28"/>
@@ -5096,10 +5122,10 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28"/>
       <c r="F59" s="28" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -5118,10 +5144,10 @@
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
       <c r="F60" s="28" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H60" s="2">
         <v>3</v>
@@ -5141,7 +5167,7 @@
       <c r="E61" s="28"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -5205,171 +5231,171 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="84" t="s">
-        <v>32</v>
+      <c r="A2" s="85" t="s">
+        <v>34</v>
       </c>
       <c r="B2" s="72" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="84" t="s">
-        <v>45</v>
+      <c r="A3" s="85" t="s">
+        <v>47</v>
       </c>
       <c r="B3" s="72" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="84" t="s">
-        <v>216</v>
+      <c r="A4" s="85" t="s">
+        <v>218</v>
       </c>
       <c r="B4" s="72" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="84" t="s">
-        <v>218</v>
+      <c r="A5" s="85" t="s">
+        <v>220</v>
       </c>
       <c r="B5" s="72" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="84" t="s">
-        <v>220</v>
+      <c r="A6" s="85" t="s">
+        <v>222</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="84" t="s">
-        <v>222</v>
+      <c r="A7" s="85" t="s">
+        <v>224</v>
       </c>
       <c r="B7" s="72" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="84" t="s">
-        <v>157</v>
+      <c r="A8" s="85" t="s">
+        <v>159</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="84" t="s">
-        <v>225</v>
+      <c r="A9" s="85" t="s">
+        <v>227</v>
       </c>
       <c r="B9" s="72" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="84" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>228</v>
+      <c r="A10" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>229</v>
+      <c r="A11" s="85" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="84" t="s">
-        <v>230</v>
+      <c r="A12" s="85" t="s">
+        <v>232</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="84" t="s">
-        <v>232</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>233</v>
+      <c r="A13" s="85" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="84" t="s">
-        <v>234</v>
-      </c>
-      <c r="B14" s="85" t="s">
-        <v>235</v>
+      <c r="A14" s="85" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" s="86" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="84" t="s">
-        <v>236</v>
-      </c>
-      <c r="B15" s="85" t="s">
-        <v>237</v>
+      <c r="A15" s="85" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" s="86" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="85" t="s">
-        <v>238</v>
+      <c r="A16" s="85" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="86" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="84" t="s">
-        <v>60</v>
+      <c r="A17" s="85" t="s">
+        <v>62</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="84" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" s="85" t="s">
-        <v>241</v>
+      <c r="A18" s="85" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="84" t="s">
-        <v>242</v>
-      </c>
-      <c r="B19" s="85" t="s">
-        <v>243</v>
+      <c r="A19" s="85" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="86" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="84" t="s">
-        <v>244</v>
-      </c>
-      <c r="B20" s="85" t="s">
-        <v>245</v>
+      <c r="A20" s="85" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" s="86" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="86" t="s">
-        <v>246</v>
+      <c r="B21" s="87" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="84" t="s">
-        <v>247</v>
-      </c>
-      <c r="B22" s="85" t="s">
-        <v>248</v>
+      <c r="A22" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" s="86" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5378,6 +5404,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5386,7 +5423,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -5641,25 +5678,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F11A6E-3447-4DD8-8640-39E570D1D2DD}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB90B757-2575-41DD-87F4-EC29D9CB0158}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8692E424-3869-4127-BDA0-1CE08A12E29A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F11A6E-3447-4DD8-8640-39E570D1D2DD}"/>
 </file>
--- a/01_Input/00_CO Validation/South Africa - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/South Africa - Energy Projects.xlsx
@@ -599,10 +599,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -691,6 +691,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1854,9 +1874,8 @@
         </is>
       </c>
       <c r="N14" s="36" t="n"/>
-      <c r="O14" s="39">
-        <f>45/84</f>
-        <v/>
+      <c r="O14" s="39" t="n">
+        <v>0.5357142857142857</v>
       </c>
       <c r="P14" s="44" t="n"/>
       <c r="Q14" s="78" t="inlineStr">
@@ -2075,15 +2094,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K19" s="65" t="n">
+      <c r="K19" s="92" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="92" t="n"/>
-      <c r="M19" s="93" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L19" s="93" t="n"/>
+      <c r="M19" s="2" t="n"/>
       <c r="N19" s="36" t="n"/>
       <c r="O19" s="38" t="n"/>
       <c r="P19" s="44" t="n"/>
@@ -2112,7 +2127,7 @@
       <c r="X20" s="4" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -2143,17 +2158,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
